--- a/data/trans_dic/P04D$colectiva-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P04D$colectiva-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción colectiva en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción colectiva en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 9,39</t>
+          <t>4,49; 9,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 10,72</t>
+          <t>5,17; 10,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,64; 16,72</t>
+          <t>10,64; 16,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,31</t>
+          <t>3,19; 8,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 8,87</t>
+          <t>3,58; 8,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,31; 17,39</t>
+          <t>11,35; 17,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,04</t>
+          <t>4,42; 8,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,96</t>
+          <t>5,16; 9,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,75; 15,82</t>
+          <t>11,9; 16,07</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,4</t>
+          <t>1,64; 5,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,21</t>
+          <t>2,77; 7,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,74</t>
+          <t>4,31; 8,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,66</t>
+          <t>2,02; 5,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,44</t>
+          <t>1,99; 6,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 8,58</t>
+          <t>4,48; 8,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,94</t>
+          <t>2,12; 4,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,86</t>
+          <t>2,87; 5,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 7,93</t>
+          <t>4,82; 7,78</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,53</t>
+          <t>1,06; 3,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,53</t>
+          <t>1,05; 3,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 6,43</t>
+          <t>1,16; 6,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 7,13</t>
+          <t>1,58; 6,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,41</t>
+          <t>0,52; 4,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 11,64</t>
+          <t>4,66; 11,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,6</t>
+          <t>1,52; 3,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,22</t>
+          <t>1,12; 3,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,0</t>
+          <t>1,6; 7,15</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,97</t>
+          <t>2,04; 4,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,77</t>
+          <t>0,57; 1,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,92</t>
+          <t>3,25; 6,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,27 +1028,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,2</t>
+          <t>0,68; 2,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,39</t>
+          <t>2,25; 6,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,48</t>
+          <t>1,94; 3,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,69</t>
+          <t>0,73; 1,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,52</t>
+          <t>3,12; 5,49</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,25</t>
+          <t>0,8; 3,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,17</t>
+          <t>0,42; 2,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,62</t>
+          <t>1,5; 4,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,05</t>
+          <t>0,98; 2,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,73</t>
+          <t>0,89; 2,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,85</t>
+          <t>1,87; 3,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,73</t>
+          <t>1,11; 2,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,11</t>
+          <t>0,86; 2,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,6</t>
+          <t>1,97; 3,66</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,31; 7,52</t>
+          <t>2,18; 7,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,04; 8,18</t>
+          <t>2,86; 7,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,33; 17,75</t>
+          <t>4,13; 16,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,34</t>
+          <t>1,63; 3,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,7</t>
+          <t>1,66; 3,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,06</t>
+          <t>3,77; 7,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,76</t>
+          <t>1,92; 3,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,24</t>
+          <t>2,22; 4,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,47; 8,37</t>
+          <t>4,42; 8,25</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,72</t>
+          <t>2,58; 3,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,43</t>
+          <t>2,26; 3,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,96</t>
+          <t>4,47; 6,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,33</t>
+          <t>2,17; 3,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,04</t>
+          <t>1,99; 3,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,64; 6,59</t>
+          <t>4,78; 6,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,34</t>
+          <t>2,52; 3,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,08</t>
+          <t>2,24; 3,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,56</t>
+          <t>4,97; 6,52</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción colectiva en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción colectiva en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19332; 41034</t>
+          <t>19641; 40086</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22132; 45977</t>
+          <t>22192; 46997</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53632; 84275</t>
+          <t>53621; 84377</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9801; 26146</t>
+          <t>10042; 25964</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12872; 30782</t>
+          <t>12439; 30244</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50435; 77576</t>
+          <t>50640; 76210</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34300; 60404</t>
+          <t>33238; 60148</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41053; 69523</t>
+          <t>40045; 69921</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>111703; 150339</t>
+          <t>113115; 152738</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6801; 22468</t>
+          <t>6847; 22068</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10447; 27180</t>
+          <t>10458; 27375</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19746; 39506</t>
+          <t>19483; 38248</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6309; 19135</t>
+          <t>6842; 20186</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7699; 23967</t>
+          <t>7399; 23755</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17040; 32834</t>
+          <t>17147; 33615</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16817; 37281</t>
+          <t>15996; 37589</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21139; 43956</t>
+          <t>21504; 44210</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40983; 66160</t>
+          <t>40250; 64989</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6776; 22214</t>
+          <t>6687; 20565</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5858; 18432</t>
+          <t>5487; 18901</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8441; 42913</t>
+          <t>7735; 45425</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4140; 18551</t>
+          <t>4117; 16569</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>880; 7318</t>
+          <t>871; 6713</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7711; 19231</t>
+          <t>7692; 19552</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13929; 32042</t>
+          <t>13534; 32747</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7559; 22171</t>
+          <t>7681; 22362</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12819; 58236</t>
+          <t>13288; 59493</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22585; 45961</t>
+          <t>23568; 46596</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6778; 20322</t>
+          <t>6498; 21058</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31841; 61084</t>
+          <t>33496; 62651</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10813; 28685</t>
+          <t>10767; 28707</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5636; 18140</t>
+          <t>5615; 19489</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23817; 62384</t>
+          <t>22008; 62851</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37990; 66858</t>
+          <t>37230; 65984</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15444; 33482</t>
+          <t>14418; 32928</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62871; 110947</t>
+          <t>62613; 110178</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4064; 16513</t>
+          <t>4083; 16216</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2627; 13441</t>
+          <t>2584; 13368</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6772; 21892</t>
+          <t>7106; 21363</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7198; 23181</t>
+          <t>7422; 22660</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5987; 20134</t>
+          <t>6541; 20552</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15842; 32332</t>
+          <t>15658; 32545</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14153; 34678</t>
+          <t>14077; 33389</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10538; 28609</t>
+          <t>11648; 29632</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25780; 47347</t>
+          <t>25907; 48021</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6156; 20004</t>
+          <t>5786; 19662</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8717; 23481</t>
+          <t>8201; 22863</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10405; 42695</t>
+          <t>9945; 40776</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17636; 36980</t>
+          <t>18095; 38727</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17751; 40079</t>
+          <t>17914; 38934</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28995; 53671</t>
+          <t>28611; 54567</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26073; 51586</t>
+          <t>26362; 52354</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>29846; 58067</t>
+          <t>30356; 56243</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>44718; 83710</t>
+          <t>44210; 82538</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>89332; 127049</t>
+          <t>88230; 129689</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>76866; 116107</t>
+          <t>76685; 116788</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>152226; 234567</t>
+          <t>150620; 231520</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76420; 118156</t>
+          <t>76958; 115668</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>70459; 107268</t>
+          <t>70133; 107902</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>165780; 235354</t>
+          <t>170554; 236938</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>175867; 232546</t>
+          <t>175604; 231176</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>156464; 212920</t>
+          <t>154647; 209459</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>348209; 454978</t>
+          <t>345031; 452661</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$colectiva-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P04D$colectiva-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 9,17</t>
+          <t>4,49; 9,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 10,95</t>
+          <t>5,08; 10,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,64; 16,74</t>
+          <t>9,86; 15,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,26</t>
+          <t>3,35; 8,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,71</t>
+          <t>3,63; 9,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,35; 17,08</t>
+          <t>11,12; 16,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,0</t>
+          <t>4,44; 7,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 9,01</t>
+          <t>5,26; 8,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,9; 16,07</t>
+          <t>11,27; 15,1</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,3</t>
+          <t>1,66; 5,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,26</t>
+          <t>2,73; 7,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 8,46</t>
+          <t>4,25; 8,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,97</t>
+          <t>1,98; 6,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,38</t>
+          <t>2,03; 6,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,79</t>
+          <t>4,54; 8,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,98</t>
+          <t>2,13; 4,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,9</t>
+          <t>2,77; 5,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 7,78</t>
+          <t>4,87; 7,81</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,27</t>
+          <t>1,12; 3,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,62</t>
+          <t>1,12; 3,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,81</t>
+          <t>4,18; 8,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,37</t>
+          <t>1,58; 7,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,04</t>
+          <t>0,52; 4,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 11,83</t>
+          <t>4,28; 11,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,68</t>
+          <t>1,52; 3,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,25</t>
+          <t>1,09; 3,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 7,15</t>
+          <t>4,88; 8,63</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,03</t>
+          <t>1,96; 4,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,83</t>
+          <t>0,59; 1,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,07</t>
+          <t>3,05; 5,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,75</t>
+          <t>1,39; 3,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,36</t>
+          <t>0,65; 2,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,44</t>
+          <t>4,38; 6,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,43</t>
+          <t>1,91; 3,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,67</t>
+          <t>0,71; 1,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 5,49</t>
+          <t>3,93; 5,76</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,19</t>
+          <t>0,94; 3,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,15</t>
+          <t>0,41; 2,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,51</t>
+          <t>1,18; 3,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,98</t>
+          <t>0,96; 3,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,78</t>
+          <t>0,93; 2,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,88</t>
+          <t>2,06; 3,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,63</t>
+          <t>1,11; 2,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,18</t>
+          <t>0,85; 2,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,66</t>
+          <t>1,98; 3,48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,39</t>
+          <t>2,23; 7,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,96</t>
+          <t>3,24; 8,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,13; 16,95</t>
+          <t>2,97; 11,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,5</t>
+          <t>1,57; 3,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,6</t>
+          <t>1,65; 3,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,77; 7,18</t>
+          <t>3,75; 6,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,81</t>
+          <t>2,0; 3,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,11</t>
+          <t>2,14; 4,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,25</t>
+          <t>3,93; 7,01</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 3,8</t>
+          <t>2,57; 3,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,45</t>
+          <t>2,22; 3,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,87</t>
+          <t>5,07; 6,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,26</t>
+          <t>2,18; 3,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,06</t>
+          <t>2,0; 3,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,78; 6,64</t>
+          <t>5,36; 6,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,32</t>
+          <t>2,52; 3,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,03</t>
+          <t>2,27; 3,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,97; 6,52</t>
+          <t>5,44; 6,55</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67546</t>
+          <t>69017</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62889</t>
+          <t>65346</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>130435</t>
+          <t>134363</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19641; 40086</t>
+          <t>19643; 42355</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22192; 46997</t>
+          <t>21819; 45909</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53621; 84377</t>
+          <t>54195; 85993</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10042; 25964</t>
+          <t>10539; 27684</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12439; 30244</t>
+          <t>12599; 32205</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50640; 76210</t>
+          <t>54162; 78145</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33238; 60148</t>
+          <t>33378; 59089</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40045; 69921</t>
+          <t>40802; 69517</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>113115; 152738</t>
+          <t>116790; 156551</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27958</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24120</t>
+          <t>26898</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>52078</t>
+          <t>55961</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6847; 22068</t>
+          <t>6925; 22621</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10458; 27375</t>
+          <t>10307; 27450</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19483; 38248</t>
+          <t>20542; 41566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6842; 20186</t>
+          <t>6705; 20702</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7399; 23755</t>
+          <t>7547; 23049</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17147; 33615</t>
+          <t>19216; 36285</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15996; 37589</t>
+          <t>16033; 35997</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21504; 44210</t>
+          <t>20765; 43335</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40250; 64989</t>
+          <t>44163; 70784</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24748</t>
+          <t>28576</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37102</t>
+          <t>41701</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6687; 20565</t>
+          <t>7049; 20842</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5487; 18901</t>
+          <t>5862; 18873</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7735; 45425</t>
+          <t>19688; 41109</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4117; 16569</t>
+          <t>4116; 18250</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>871; 6713</t>
+          <t>861; 7700</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7692; 19552</t>
+          <t>7957; 20783</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13534; 32747</t>
+          <t>13561; 33796</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7681; 22362</t>
+          <t>7514; 22148</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13288; 59493</t>
+          <t>32067; 56622</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44281</t>
+          <t>47011</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45349</t>
+          <t>47164</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>89631</t>
+          <t>94175</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23568; 46596</t>
+          <t>22675; 47231</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6498; 21058</t>
+          <t>6799; 20078</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33496; 62651</t>
+          <t>34357; 64072</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10767; 28707</t>
+          <t>10617; 29578</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5615; 19489</t>
+          <t>5346; 18388</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22008; 62851</t>
+          <t>37653; 59815</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37230; 65984</t>
+          <t>36665; 66548</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14418; 32928</t>
+          <t>14112; 32680</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62613; 110178</t>
+          <t>78078; 114368</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23292</t>
+          <t>23934</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>35800</t>
+          <t>36516</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4083; 16216</t>
+          <t>4773; 16244</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2584; 13368</t>
+          <t>2522; 13637</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7106; 21363</t>
+          <t>6712; 21299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7422; 22660</t>
+          <t>7320; 24484</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6541; 20552</t>
+          <t>6852; 21068</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15658; 32545</t>
+          <t>17092; 32881</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14077; 33389</t>
+          <t>14058; 34754</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11648; 29632</t>
+          <t>11490; 29160</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25907; 48021</t>
+          <t>27620; 48608</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20637</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39136</t>
+          <t>42724</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>59773</t>
+          <t>57869</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5786; 19662</t>
+          <t>5939; 20274</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8201; 22863</t>
+          <t>9313; 24238</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9945; 40776</t>
+          <t>7046; 28395</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18095; 38727</t>
+          <t>17344; 39197</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17914; 38934</t>
+          <t>17897; 39809</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28611; 54567</t>
+          <t>31629; 58403</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26362; 52354</t>
+          <t>27457; 51386</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30356; 56243</t>
+          <t>29351; 56812</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>44210; 82538</t>
+          <t>42438; 75707</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197679</t>
+          <t>201393</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>207140</t>
+          <t>219192</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>404819</t>
+          <t>420585</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>88230; 129689</t>
+          <t>87689; 130141</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>76685; 116788</t>
+          <t>75295; 115576</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>150620; 231520</t>
+          <t>174058; 230072</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76958; 115668</t>
+          <t>77345; 117638</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>70133; 107902</t>
+          <t>70466; 108656</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>170554; 236938</t>
+          <t>194271; 245707</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>175604; 231176</t>
+          <t>175354; 234629</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>154647; 209459</t>
+          <t>157217; 208131</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>345031; 452661</t>
+          <t>383861; 462134</t>
         </is>
       </c>
     </row>
